--- a/data/trans_orig/P1002-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1002-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de hacer algunas tareas por problemas emocionales en 2007</t>
+          <t>Población que dejo de hacer algunas tareas por problemas emocionales en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3807</t>
+          <t>3502</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17083</t>
+          <t>16593</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7533</t>
+          <t>7500</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22182</t>
+          <t>21705</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13809</t>
+          <t>13105</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32111</t>
+          <t>33554</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>476981</t>
+          <t>477471</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>490257</t>
+          <t>490562</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>445307</t>
+          <t>445784</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>459956</t>
+          <t>459989</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>929442</t>
+          <t>927999</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>947744</t>
+          <t>948448</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,64%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11122</t>
+          <t>11584</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29270</t>
+          <t>29566</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26268</t>
+          <t>26495</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51390</t>
+          <t>51995</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>41500</t>
+          <t>42211</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>73948</t>
+          <t>73885</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>706219</t>
+          <t>705923</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>724367</t>
+          <t>723905</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>574104</t>
+          <t>573499</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>599226</t>
+          <t>598999</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1287034</t>
+          <t>1287097</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1319482</t>
+          <t>1318771</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,9%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15791</t>
+          <t>16627</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38122</t>
+          <t>38160</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25227</t>
+          <t>25654</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48921</t>
+          <t>48669</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47338</t>
+          <t>48025</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79090</t>
+          <t>78392</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>600546</t>
+          <t>600508</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>622877</t>
+          <t>622041</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>640823</t>
+          <t>641075</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>664517</t>
+          <t>664090</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1249322</t>
+          <t>1250020</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1281074</t>
+          <t>1280387</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,38%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15570</t>
+          <t>15889</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35528</t>
+          <t>34851</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38512</t>
+          <t>37494</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65281</t>
+          <t>64888</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>59212</t>
+          <t>59148</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>94528</t>
+          <t>93130</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,0%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>483619</t>
+          <t>484296</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>503577</t>
+          <t>503258</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>450361</t>
+          <t>450754</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>477130</t>
+          <t>478148</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>940261</t>
+          <t>941659</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>975577</t>
+          <t>975641</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19679</t>
+          <t>19600</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40276</t>
+          <t>41297</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29119</t>
+          <t>28916</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>53026</t>
+          <t>53448</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>54597</t>
+          <t>53036</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>86498</t>
+          <t>85758</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,85%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>346434</t>
+          <t>345413</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>367031</t>
+          <t>367110</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>350960</t>
+          <t>350538</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>374867</t>
+          <t>375070</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>704198</t>
+          <t>704938</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>736099</t>
+          <t>737660</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,29%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21519</t>
+          <t>22087</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>42076</t>
+          <t>41974</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>38210</t>
+          <t>37307</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>62445</t>
+          <t>61972</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>63162</t>
+          <t>64754</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>96392</t>
+          <t>97354</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,32%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>250507</t>
+          <t>250609</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>271064</t>
+          <t>270496</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>280489</t>
+          <t>280962</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>304724</t>
+          <t>305627</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>539125</t>
+          <t>538163</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>572355</t>
+          <t>570763</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>89,81%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23944</t>
+          <t>23804</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>44783</t>
+          <t>45063</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>47733</t>
+          <t>47324</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>79738</t>
+          <t>77478</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>78230</t>
+          <t>77231</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>116059</t>
+          <t>115509</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,24%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>165100</t>
+          <t>164820</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>185939</t>
+          <t>186079</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>254170</t>
+          <t>256430</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>286175</t>
+          <t>286584</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>427732</t>
+          <t>428282</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>465561</t>
+          <t>466560</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,8%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>146413</t>
+          <t>146756</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>197135</t>
+          <t>198797</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>253234</t>
+          <t>254321</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>321680</t>
+          <t>320284</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>416591</t>
+          <t>416760</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>501248</t>
+          <t>498152</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3079408</t>
+          <t>3077746</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3130130</t>
+          <t>3129787</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3057517</t>
+          <t>3058913</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3125963</t>
+          <t>3124876</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6154493</t>
+          <t>6157589</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6239150</t>
+          <t>6238981</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de hacer algunas tareas por problemas emocionales en 2012</t>
+          <t>Población que dejo de hacer algunas tareas por problemas emocionales en 2012 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4550</t>
+          <t>4620</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15984</t>
+          <t>16526</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11709</t>
+          <t>11990</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28642</t>
+          <t>29711</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18815</t>
+          <t>19256</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40372</t>
+          <t>40092</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>438162</t>
+          <t>437620</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>449596</t>
+          <t>449526</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>401588</t>
+          <t>400519</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>418521</t>
+          <t>418240</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>844004</t>
+          <t>844284</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>865561</t>
+          <t>865120</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,82%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11101</t>
+          <t>10573</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30937</t>
+          <t>28664</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21387</t>
+          <t>20400</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43310</t>
+          <t>43588</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37319</t>
+          <t>36200</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>65877</t>
+          <t>64597</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>656150</t>
+          <t>658423</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>675986</t>
+          <t>676514</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>566945</t>
+          <t>566667</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>588868</t>
+          <t>589855</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1231465</t>
+          <t>1232745</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1260023</t>
+          <t>1261142</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,21%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20448</t>
+          <t>20207</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43428</t>
+          <t>44117</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>65192</t>
+          <t>62937</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>99956</t>
+          <t>96991</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>91113</t>
+          <t>89752</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>133261</t>
+          <t>131079</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,42%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>637498</t>
+          <t>636809</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>660478</t>
+          <t>660719</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>610894</t>
+          <t>613859</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>645658</t>
+          <t>647913</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1258514</t>
+          <t>1260696</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1300662</t>
+          <t>1302023</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,55%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28290</t>
+          <t>28140</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56301</t>
+          <t>57284</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>64394</t>
+          <t>63975</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>97804</t>
+          <t>98862</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>99765</t>
+          <t>98284</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>145888</t>
+          <t>142267</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>557262</t>
+          <t>556279</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>585273</t>
+          <t>585423</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>518395</t>
+          <t>517337</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>551805</t>
+          <t>552224</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1083874</t>
+          <t>1087495</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1129997</t>
+          <t>1131478</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>92,01%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28169</t>
+          <t>27900</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>53118</t>
+          <t>51489</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>72596</t>
+          <t>71895</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>105551</t>
+          <t>104517</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>106856</t>
+          <t>107780</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>149854</t>
+          <t>148911</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,0%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>376311</t>
+          <t>377940</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>401260</t>
+          <t>401529</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>341194</t>
+          <t>342228</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>374149</t>
+          <t>374850</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>726320</t>
+          <t>727263</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>769318</t>
+          <t>768394</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,7%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>28772</t>
+          <t>28329</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>52591</t>
+          <t>54606</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>61360</t>
+          <t>62231</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>92215</t>
+          <t>91189</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>95508</t>
+          <t>94603</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>134734</t>
+          <t>135013</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,37%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>257195</t>
+          <t>255180</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>281014</t>
+          <t>281457</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>260836</t>
+          <t>261862</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>291691</t>
+          <t>290820</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>528103</t>
+          <t>527824</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>567329</t>
+          <t>568234</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,73%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>40405</t>
+          <t>40880</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>69523</t>
+          <t>68418</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,82 +5785,82 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>27,38%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>124081</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>104588</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>143311</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>31,9%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>26,89%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>36,84%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>177801</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>156404</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>202957</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
           <t>27,83%</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>124081</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>104642</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>143777</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>31,9%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>26,9%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>36,96%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>177801</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>154410</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>201479</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>27,83%</t>
-        </is>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,77%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>180328</t>
+          <t>181433</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>209446</t>
+          <t>208971</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,82 +5898,82 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
+          <t>72,62%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>83,64%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>264898</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>245668</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>284391</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>68,1%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>63,16%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>73,11%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>461029</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>435873</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>482426</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
           <t>72,17%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>83,83%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>264898</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>245202</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>284337</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>68,1%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>63,04%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>73,1%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>461029</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>437351</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>484420</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>72,17%</t>
-        </is>
-      </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>68,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>75,52%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>202429</t>
+          <t>200223</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>265576</t>
+          <t>262762</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>458056</t>
+          <t>458486</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>540116</t>
+          <t>543955</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>674567</t>
+          <t>676277</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>780114</t>
+          <t>777108</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,13%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3159212</t>
+          <t>3162026</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3222359</t>
+          <t>3224565</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3016193</t>
+          <t>3012354</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3098253</t>
+          <t>3097823</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6200983</t>
+          <t>6203989</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6306530</t>
+          <t>6304820</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,31%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de hacer algunas tareas por problemas emocionales en 2016</t>
+          <t>Población que dejo de hacer algunas tareas por problemas emocionales en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4267</t>
+          <t>4304</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16990</t>
+          <t>17025</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4024</t>
+          <t>4720</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16085</t>
+          <t>16653</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11239</t>
+          <t>11343</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27939</t>
+          <t>28193</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>402473</t>
+          <t>402438</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>415196</t>
+          <t>415159</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>379670</t>
+          <t>379102</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>391731</t>
+          <t>391035</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>787279</t>
+          <t>787025</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>803979</t>
+          <t>803875</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13644</t>
+          <t>13550</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34220</t>
+          <t>33697</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14159</t>
+          <t>13928</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32256</t>
+          <t>32040</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32526</t>
+          <t>32080</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>58239</t>
+          <t>59019</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>556276</t>
+          <t>556799</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>576852</t>
+          <t>576946</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>531288</t>
+          <t>531504</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>549385</t>
+          <t>549616</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1095801</t>
+          <t>1095021</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1121514</t>
+          <t>1121960</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,22%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14074</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33817</t>
+          <t>33508</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28630</t>
+          <t>28106</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53327</t>
+          <t>51874</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>48347</t>
+          <t>48256</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>80161</t>
+          <t>78908</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>635280</t>
+          <t>635589</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>655023</t>
+          <t>654666</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>608059</t>
+          <t>609512</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>632756</t>
+          <t>633280</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1250322</t>
+          <t>1251575</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1282136</t>
+          <t>1282227</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29848</t>
+          <t>28159</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>55910</t>
+          <t>54219</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47977</t>
+          <t>49725</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>79377</t>
+          <t>78759</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>83753</t>
+          <t>83436</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>123395</t>
+          <t>124020</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>590138</t>
+          <t>591829</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>616200</t>
+          <t>617889</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>569700</t>
+          <t>570318</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>601100</t>
+          <t>599352</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1171730</t>
+          <t>1171105</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1211372</t>
+          <t>1211689</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,56%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18449</t>
+          <t>18187</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39460</t>
+          <t>39257</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>64306</t>
+          <t>63107</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>98624</t>
+          <t>97298</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>87294</t>
+          <t>87740</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>129971</t>
+          <t>128802</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,21%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>438458</t>
+          <t>438661</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>459469</t>
+          <t>459731</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>398225</t>
+          <t>399551</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>432543</t>
+          <t>433742</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>844796</t>
+          <t>845965</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>887473</t>
+          <t>887027</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>91,0%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20165</t>
+          <t>20572</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>41541</t>
+          <t>41482</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>52353</t>
+          <t>54176</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>82677</t>
+          <t>83349</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>78781</t>
+          <t>80220</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>115213</t>
+          <t>118444</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,63%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>292789</t>
+          <t>292848</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>314165</t>
+          <t>313758</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>295085</t>
+          <t>294413</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>325409</t>
+          <t>323586</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>596879</t>
+          <t>593648</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>633311</t>
+          <t>631872</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>88,73%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21242</t>
+          <t>22166</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40606</t>
+          <t>40859</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>78270</t>
+          <t>78999</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>118493</t>
+          <t>118284</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>106815</t>
+          <t>107679</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>153333</t>
+          <t>153497</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,36%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>216392</t>
+          <t>216139</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>235756</t>
+          <t>234832</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>281676</t>
+          <t>281885</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>321899</t>
+          <t>321170</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>503834</t>
+          <t>503670</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>550352</t>
+          <t>549488</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,61%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>157335</t>
+          <t>155036</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>209501</t>
+          <t>210026</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>341007</t>
+          <t>342362</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>415129</t>
+          <t>420308</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>512014</t>
+          <t>512495</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>603749</t>
+          <t>607279</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3184849</t>
+          <t>3184324</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3237015</t>
+          <t>3239314</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3129413</t>
+          <t>3124234</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3203535</t>
+          <t>3202180</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6335143</t>
+          <t>6331613</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6426878</t>
+          <t>6426397</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,61%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de hacer algunas tareas por problemas emocionales en 2023</t>
+          <t>Población que dejo de hacer algunas tareas por problemas emocionales en 2023 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16846</t>
+          <t>19619</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9046</t>
+          <t>8313</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34388</t>
+          <t>33341</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11262</t>
+          <t>10595</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39813</t>
+          <t>37690</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -9783,7 +9783,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>383141</t>
+          <t>380368</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>278812</t>
+          <t>279859</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>304154</t>
+          <t>304887</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>673374</t>
+          <t>675497</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>701925</t>
+          <t>702592</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,51%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5525</t>
+          <t>5026</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25675</t>
+          <t>25844</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14111</t>
+          <t>14578</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41835</t>
+          <t>41574</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26849</t>
+          <t>26368</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>59359</t>
+          <t>59883</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>397872</t>
+          <t>397703</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>418022</t>
+          <t>418521</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>469669</t>
+          <t>469930</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>497393</t>
+          <t>496926</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>875692</t>
+          <t>875168</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>908202</t>
+          <t>908683</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,18%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18871</t>
+          <t>18852</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41675</t>
+          <t>41554</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21573</t>
+          <t>21493</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39075</t>
+          <t>38736</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44255</t>
+          <t>44916</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>72381</t>
+          <t>73447</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>494663</t>
+          <t>494784</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>517467</t>
+          <t>517486</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>503393</t>
+          <t>503732</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>520895</t>
+          <t>520975</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1006425</t>
+          <t>1005359</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1034551</t>
+          <t>1033890</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,84%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17689</t>
+          <t>16787</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65311</t>
+          <t>64930</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48539</t>
+          <t>46983</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>80580</t>
+          <t>79099</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>58819</t>
+          <t>65104</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>133625</t>
+          <t>134468</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>822475</t>
+          <t>822856</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>870097</t>
+          <t>870999</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>632301</t>
+          <t>633782</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>664342</t>
+          <t>665898</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1467042</t>
+          <t>1466199</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1541848</t>
+          <t>1535563</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>95,93%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33720</t>
+          <t>33195</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>57307</t>
+          <t>57205</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>56922</t>
+          <t>57581</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>79667</t>
+          <t>80678</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>94601</t>
+          <t>95991</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>128524</t>
+          <t>129856</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,71%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>503927</t>
+          <t>504029</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>527514</t>
+          <t>528039</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>467916</t>
+          <t>466905</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>490661</t>
+          <t>490002</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>980293</t>
+          <t>978961</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1014216</t>
+          <t>1012826</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,34%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19602</t>
+          <t>20572</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35952</t>
+          <t>36422</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22801</t>
+          <t>23049</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>89450</t>
+          <t>89538</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>40698</t>
+          <t>39704</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>111064</t>
+          <t>111175</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,39%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>331643</t>
+          <t>331173</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>347993</t>
+          <t>347023</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>518918</t>
+          <t>518830</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>585567</t>
+          <t>585319</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>864899</t>
+          <t>864788</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>935265</t>
+          <t>936259</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,93%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22903</t>
+          <t>23350</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40275</t>
+          <t>39817</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>92448</t>
+          <t>91937</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>119368</t>
+          <t>116995</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>119911</t>
+          <t>120099</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>150416</t>
+          <t>151039</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,38%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>241848</t>
+          <t>242306</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>259220</t>
+          <t>258773</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>304955</t>
+          <t>307328</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>331875</t>
+          <t>332386</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>78,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>556031</t>
+          <t>555408</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>586536</t>
+          <t>586348</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>83,0%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>143983</t>
+          <t>144095</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>218652</t>
+          <t>218060</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>297598</t>
+          <t>293952</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>405500</t>
+          <t>409591</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>477718</t>
+          <t>480796</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>608844</t>
+          <t>614848</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3239959</t>
+          <t>3240551</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3314628</t>
+          <t>3314516</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3254827</t>
+          <t>3250736</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3362729</t>
+          <t>3366375</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6510094</t>
+          <t>6504090</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6641220</t>
+          <t>6638142</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,25%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1002-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1002-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3502</t>
+          <t>3233</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16593</t>
+          <t>16118</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7500</t>
+          <t>7393</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21705</t>
+          <t>22133</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13105</t>
+          <t>13944</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33554</t>
+          <t>34592</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>477471</t>
+          <t>477946</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>490562</t>
+          <t>490831</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>445784</t>
+          <t>445356</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>459989</t>
+          <t>460096</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>927999</t>
+          <t>926961</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>948448</t>
+          <t>947609</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,55%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11584</t>
+          <t>11973</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29566</t>
+          <t>29487</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26495</t>
+          <t>28153</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51995</t>
+          <t>51503</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42211</t>
+          <t>43108</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>73885</t>
+          <t>75090</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>705923</t>
+          <t>706002</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>723905</t>
+          <t>723516</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>573499</t>
+          <t>573991</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>598999</t>
+          <t>597341</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1287097</t>
+          <t>1285892</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1318771</t>
+          <t>1317874</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,83%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16627</t>
+          <t>17290</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38160</t>
+          <t>39535</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25654</t>
+          <t>24485</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48669</t>
+          <t>48434</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>48025</t>
+          <t>46878</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>78392</t>
+          <t>77584</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>600508</t>
+          <t>599133</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>622041</t>
+          <t>621378</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>641075</t>
+          <t>641310</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>664090</t>
+          <t>665259</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1250020</t>
+          <t>1250828</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1280387</t>
+          <t>1281534</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,47%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15889</t>
+          <t>15682</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34851</t>
+          <t>35789</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37494</t>
+          <t>37679</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>64888</t>
+          <t>65698</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>59148</t>
+          <t>59370</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>93130</t>
+          <t>91281</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>484296</t>
+          <t>483358</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>503258</t>
+          <t>503465</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>450754</t>
+          <t>449944</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>478148</t>
+          <t>477963</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>941659</t>
+          <t>943508</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>975641</t>
+          <t>975419</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,26%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19600</t>
+          <t>19638</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41297</t>
+          <t>38629</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28916</t>
+          <t>29716</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>53448</t>
+          <t>53354</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>53036</t>
+          <t>54710</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>85758</t>
+          <t>87303</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,04%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>345413</t>
+          <t>348081</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>367110</t>
+          <t>367072</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>350538</t>
+          <t>350632</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>375070</t>
+          <t>374270</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>704938</t>
+          <t>703393</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>737660</t>
+          <t>735986</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,08%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22087</t>
+          <t>21448</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>41974</t>
+          <t>41525</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>37307</t>
+          <t>36985</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>61972</t>
+          <t>61319</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>64754</t>
+          <t>64052</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>97354</t>
+          <t>96050</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,11%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>250609</t>
+          <t>251058</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>270496</t>
+          <t>271135</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>280962</t>
+          <t>281615</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>305627</t>
+          <t>305949</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>538163</t>
+          <t>539467</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>570763</t>
+          <t>571465</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,92%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23804</t>
+          <t>25136</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45063</t>
+          <t>45572</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>47324</t>
+          <t>47149</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>77478</t>
+          <t>77793</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>77231</t>
+          <t>79998</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>115509</t>
+          <t>114448</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,05%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>164820</t>
+          <t>164311</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>186079</t>
+          <t>184747</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>256430</t>
+          <t>256115</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>286584</t>
+          <t>286759</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>76,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>428282</t>
+          <t>429343</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>466560</t>
+          <t>463793</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>85,29%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>146756</t>
+          <t>148464</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>198797</t>
+          <t>198912</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>254321</t>
+          <t>256407</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>320284</t>
+          <t>320052</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>416760</t>
+          <t>417963</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>498152</t>
+          <t>503940</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3077746</t>
+          <t>3077631</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3129787</t>
+          <t>3128079</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3058913</t>
+          <t>3059145</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3124876</t>
+          <t>3122790</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6157589</t>
+          <t>6151801</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6238981</t>
+          <t>6237778</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,72%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4620</t>
+          <t>4671</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16526</t>
+          <t>15861</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11990</t>
+          <t>12440</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29711</t>
+          <t>29627</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19256</t>
+          <t>19169</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40092</t>
+          <t>39652</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>437620</t>
+          <t>438285</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>449526</t>
+          <t>449475</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>400519</t>
+          <t>400603</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>418240</t>
+          <t>417790</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>844284</t>
+          <t>844724</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>865120</t>
+          <t>865207</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,83%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10573</t>
+          <t>10781</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28664</t>
+          <t>28580</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20400</t>
+          <t>20995</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43588</t>
+          <t>43451</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36200</t>
+          <t>36500</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>64597</t>
+          <t>66319</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>658423</t>
+          <t>658507</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>676514</t>
+          <t>676306</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>566667</t>
+          <t>566804</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>589855</t>
+          <t>589260</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1232745</t>
+          <t>1231023</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1261142</t>
+          <t>1260842</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,19%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20207</t>
+          <t>21280</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44117</t>
+          <t>44075</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>62937</t>
+          <t>62402</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>96991</t>
+          <t>98753</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>89752</t>
+          <t>88962</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>131079</t>
+          <t>131521</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>636809</t>
+          <t>636851</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>660719</t>
+          <t>659646</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>613859</t>
+          <t>612097</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>647913</t>
+          <t>648448</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1260696</t>
+          <t>1260254</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1302023</t>
+          <t>1302813</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,61%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28140</t>
+          <t>28483</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57284</t>
+          <t>55842</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>63975</t>
+          <t>63039</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>98862</t>
+          <t>98901</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>98284</t>
+          <t>100054</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>142267</t>
+          <t>143975</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,71%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>556279</t>
+          <t>557721</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>585423</t>
+          <t>585080</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>517337</t>
+          <t>517298</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>552224</t>
+          <t>553160</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1087495</t>
+          <t>1085787</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1131478</t>
+          <t>1129708</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>91,86%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27900</t>
+          <t>28726</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51489</t>
+          <t>52625</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>71895</t>
+          <t>70857</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>104517</t>
+          <t>106514</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>107780</t>
+          <t>108542</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>148911</t>
+          <t>151085</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,24%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>377940</t>
+          <t>376804</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>401529</t>
+          <t>400703</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>342228</t>
+          <t>340231</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>374850</t>
+          <t>375888</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>727263</t>
+          <t>725089</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>768394</t>
+          <t>767632</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,61%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>28329</t>
+          <t>27345</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>54606</t>
+          <t>52810</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>62231</t>
+          <t>60187</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>91189</t>
+          <t>90705</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>94603</t>
+          <t>96815</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>135013</t>
+          <t>135985</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,52%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>255180</t>
+          <t>256976</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>281457</t>
+          <t>282441</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>261862</t>
+          <t>262346</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>290820</t>
+          <t>292864</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>74,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>527824</t>
+          <t>526852</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>568234</t>
+          <t>566022</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,39%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>40880</t>
+          <t>41626</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>68418</t>
+          <t>69738</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>104588</t>
+          <t>104438</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>143311</t>
+          <t>143970</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>156404</t>
+          <t>155941</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>202957</t>
+          <t>203124</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,8%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>181433</t>
+          <t>180113</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>208971</t>
+          <t>208225</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>245668</t>
+          <t>245009</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>284391</t>
+          <t>284541</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>62,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>435873</t>
+          <t>435706</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>482426</t>
+          <t>482889</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>75,59%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>200223</t>
+          <t>203429</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>262762</t>
+          <t>264601</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>458486</t>
+          <t>458375</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>543955</t>
+          <t>538013</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>676277</t>
+          <t>677517</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>777108</t>
+          <t>780673</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,18%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3162026</t>
+          <t>3160187</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3224565</t>
+          <t>3221359</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3012354</t>
+          <t>3018296</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3097823</t>
+          <t>3097934</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6203989</t>
+          <t>6200424</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6304820</t>
+          <t>6303580</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,29%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4304</t>
+          <t>4330</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17025</t>
+          <t>16747</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4720</t>
+          <t>4137</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16653</t>
+          <t>15943</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11343</t>
+          <t>11035</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28193</t>
+          <t>28280</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>402438</t>
+          <t>402716</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>415159</t>
+          <t>415133</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>379102</t>
+          <t>379812</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>391035</t>
+          <t>391618</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>787025</t>
+          <t>786938</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>803875</t>
+          <t>804183</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13550</t>
+          <t>14071</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33697</t>
+          <t>33636</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13928</t>
+          <t>14141</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32040</t>
+          <t>32037</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32080</t>
+          <t>32122</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>59019</t>
+          <t>58501</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>556799</t>
+          <t>556860</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>576946</t>
+          <t>576425</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>531504</t>
+          <t>531507</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>549616</t>
+          <t>549403</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1095021</t>
+          <t>1095539</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1121960</t>
+          <t>1121918</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>14720</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33508</t>
+          <t>34399</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28106</t>
+          <t>28593</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51874</t>
+          <t>53000</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>48256</t>
+          <t>47672</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>78908</t>
+          <t>77705</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>635589</t>
+          <t>634698</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>654666</t>
+          <t>654377</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>609512</t>
+          <t>608386</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>633280</t>
+          <t>632793</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1251575</t>
+          <t>1252778</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1282227</t>
+          <t>1282811</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,42%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28159</t>
+          <t>29397</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54219</t>
+          <t>54314</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49725</t>
+          <t>49067</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>78759</t>
+          <t>79938</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>83436</t>
+          <t>83882</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>124020</t>
+          <t>126096</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>591829</t>
+          <t>591734</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>617889</t>
+          <t>616651</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>570318</t>
+          <t>569139</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>599352</t>
+          <t>600010</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1171105</t>
+          <t>1169029</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1211689</t>
+          <t>1211243</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,52%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18187</t>
+          <t>17694</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39257</t>
+          <t>39852</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>63107</t>
+          <t>63404</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>97298</t>
+          <t>98147</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>87740</t>
+          <t>88573</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>128802</t>
+          <t>130290</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,37%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>438661</t>
+          <t>438066</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>459731</t>
+          <t>460224</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>399551</t>
+          <t>398702</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>433742</t>
+          <t>433445</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>845965</t>
+          <t>844477</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>887027</t>
+          <t>886194</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>90,91%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20572</t>
+          <t>20364</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>41482</t>
+          <t>42166</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>54176</t>
+          <t>52806</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>83349</t>
+          <t>83510</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>80220</t>
+          <t>80677</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>118444</t>
+          <t>118061</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,58%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>292848</t>
+          <t>292164</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>313758</t>
+          <t>313966</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>294413</t>
+          <t>294252</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>323586</t>
+          <t>324956</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>593648</t>
+          <t>594031</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>631872</t>
+          <t>631415</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,67%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22166</t>
+          <t>20944</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40859</t>
+          <t>40225</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>78999</t>
+          <t>79006</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>118284</t>
+          <t>117248</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8804,7 +8804,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>107679</t>
+          <t>108990</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>153497</t>
+          <t>153902</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,42%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>216139</t>
+          <t>216773</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>234832</t>
+          <t>236054</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>281885</t>
+          <t>282921</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>321170</t>
+          <t>321163</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,7 +8912,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>503670</t>
+          <t>503265</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>549488</t>
+          <t>548177</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,42%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>155036</t>
+          <t>158177</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>210026</t>
+          <t>210644</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>342362</t>
+          <t>337941</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>420308</t>
+          <t>419802</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>512495</t>
+          <t>514784</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>607279</t>
+          <t>607076</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,7 +9177,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3184324</t>
+          <t>3183706</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3239314</t>
+          <t>3236173</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3124234</t>
+          <t>3124740</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3202180</t>
+          <t>3206601</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6331613</t>
+          <t>6331816</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6426397</t>
+          <t>6424108</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9295,7 +9295,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,58%</t>
         </is>
       </c>
     </row>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>4766</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -9675,12 +9675,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19619</t>
+          <t>16006</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>18577</t>
+          <t>21527</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8313</t>
+          <t>10868</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33341</t>
+          <t>39453</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>22021</t>
+          <t>26293</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10595</t>
+          <t>13246</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37690</t>
+          <t>44010</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -9778,27 +9778,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>396544</t>
+          <t>403027</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>380368</t>
+          <t>391787</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>294623</t>
+          <t>340985</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>279859</t>
+          <t>323059</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>304887</t>
+          <t>351644</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>691166</t>
+          <t>744012</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>675497</t>
+          <t>726295</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>702592</t>
+          <t>757059</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,28%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12466</t>
+          <t>14408</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5026</t>
+          <t>5757</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25844</t>
+          <t>29510</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>27139</t>
+          <t>29014</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14578</t>
+          <t>19032</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41574</t>
+          <t>45242</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>39605</t>
+          <t>43422</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26368</t>
+          <t>28818</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>59883</t>
+          <t>61126</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>411081</t>
+          <t>462482</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>397703</t>
+          <t>447380</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>418521</t>
+          <t>471133</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>484365</t>
+          <t>472069</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>469930</t>
+          <t>455841</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>496926</t>
+          <t>482051</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>895446</t>
+          <t>934551</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>875168</t>
+          <t>916847</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>908683</t>
+          <t>949155</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,05%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>28577</t>
+          <t>30366</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18852</t>
+          <t>20330</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41554</t>
+          <t>44209</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>29140</t>
+          <t>33333</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21493</t>
+          <t>24393</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38736</t>
+          <t>43670</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>57718</t>
+          <t>63700</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44916</t>
+          <t>50422</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>73447</t>
+          <t>79223</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>507761</t>
+          <t>590471</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>494784</t>
+          <t>576628</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>517486</t>
+          <t>600507</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>513328</t>
+          <t>588806</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>503732</t>
+          <t>578469</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>520975</t>
+          <t>597746</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1021088</t>
+          <t>1179276</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1005359</t>
+          <t>1163753</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1033890</t>
+          <t>1192554</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,94%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>41820</t>
+          <t>43366</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16787</t>
+          <t>31000</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64930</t>
+          <t>59765</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>61505</t>
+          <t>61251</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46983</t>
+          <t>49304</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>79099</t>
+          <t>73681</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>103324</t>
+          <t>104617</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>65104</t>
+          <t>86651</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>134468</t>
+          <t>123336</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>845966</t>
+          <t>657251</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>822856</t>
+          <t>640852</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>870999</t>
+          <t>669617</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>651376</t>
+          <t>675635</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>633782</t>
+          <t>663205</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>665898</t>
+          <t>687582</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1497343</t>
+          <t>1332887</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1466199</t>
+          <t>1314168</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1535563</t>
+          <t>1350853</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>93,97%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>43278</t>
+          <t>44672</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33195</t>
+          <t>33415</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>57205</t>
+          <t>58170</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>68127</t>
+          <t>77455</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>57581</t>
+          <t>66021</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>80678</t>
+          <t>92403</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>111405</t>
+          <t>122127</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>95991</t>
+          <t>105924</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>129856</t>
+          <t>139899</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,49%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>517956</t>
+          <t>564674</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>504029</t>
+          <t>551176</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>528039</t>
+          <t>575931</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>479456</t>
+          <t>531082</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>466905</t>
+          <t>516134</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>490002</t>
+          <t>542516</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>997412</t>
+          <t>1095756</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>978961</t>
+          <t>1077984</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1012826</t>
+          <t>1111959</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,3%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547583</t>
+          <t>608537</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547583</t>
+          <t>608537</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547583</t>
+          <t>608537</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1108817</t>
+          <t>1217883</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1108817</t>
+          <t>1217883</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1108817</t>
+          <t>1217883</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>27789</t>
+          <t>30281</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20572</t>
+          <t>22910</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36422</t>
+          <t>40520</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>56096</t>
+          <t>63430</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23049</t>
+          <t>52666</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>89538</t>
+          <t>73765</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>83885</t>
+          <t>93711</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>39704</t>
+          <t>79480</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>111175</t>
+          <t>108264</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>12,8%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>339806</t>
+          <t>376212</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>331173</t>
+          <t>365973</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>347023</t>
+          <t>383583</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>552272</t>
+          <t>375736</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>518830</t>
+          <t>365401</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>585319</t>
+          <t>386500</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>892078</t>
+          <t>751949</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>864788</t>
+          <t>737396</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>936259</t>
+          <t>766180</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>90,6%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>367595</t>
+          <t>406493</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>367595</t>
+          <t>406493</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>367595</t>
+          <t>406493</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>975963</t>
+          <t>845660</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>975963</t>
+          <t>845660</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>975963</t>
+          <t>845660</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>30462</t>
+          <t>35113</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23350</t>
+          <t>26696</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39817</t>
+          <t>45428</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>104572</t>
+          <t>116792</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>91937</t>
+          <t>102889</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>116995</t>
+          <t>130682</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>135034</t>
+          <t>151905</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>120099</t>
+          <t>136044</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>151039</t>
+          <t>170786</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>22,11%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>251661</t>
+          <t>274470</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>242306</t>
+          <t>264155</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>258773</t>
+          <t>282887</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>319751</t>
+          <t>346233</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>307328</t>
+          <t>332343</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>332386</t>
+          <t>360136</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>571413</t>
+          <t>620702</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>555408</t>
+          <t>601821</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>586348</t>
+          <t>636563</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>82,39%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282123</t>
+          <t>309583</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282123</t>
+          <t>309583</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282123</t>
+          <t>309583</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>424323</t>
+          <t>463025</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>424323</t>
+          <t>463025</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>424323</t>
+          <t>463025</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>706447</t>
+          <t>772607</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>706447</t>
+          <t>772607</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>706447</t>
+          <t>772607</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>187834</t>
+          <t>202972</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>144095</t>
+          <t>176467</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>218060</t>
+          <t>233558</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>365157</t>
+          <t>402803</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>293952</t>
+          <t>372575</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>409591</t>
+          <t>438334</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
+          <t>10,79%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
           <t>9,98%</t>
         </is>
       </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>8,03%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>552991</t>
+          <t>605775</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>480796</t>
+          <t>560588</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>614848</t>
+          <t>646768</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,9%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3270777</t>
+          <t>3328588</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3240551</t>
+          <t>3298002</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3314516</t>
+          <t>3355093</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,34 +12214,34 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3295170</t>
+          <t>3330545</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3250736</t>
+          <t>3295014</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3366375</t>
+          <t>3360773</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
+          <t>89,21%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>88,26%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
           <t>90,02%</t>
         </is>
       </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>88,81%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>91,97%</t>
-        </is>
-      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>7912</t>
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6565947</t>
+          <t>6659134</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6504090</t>
+          <t>6618141</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6638142</t>
+          <t>6704321</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>92,28%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3458611</t>
+          <t>3531560</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3458611</t>
+          <t>3531560</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3458611</t>
+          <t>3531560</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3660327</t>
+          <t>3733348</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3660327</t>
+          <t>3733348</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3660327</t>
+          <t>3733348</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7118938</t>
+          <t>7264909</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7118938</t>
+          <t>7264909</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7118938</t>
+          <t>7264909</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
